--- a/AAII_Financials/Yearly/QNCX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/QNCX_YR_FIN.xlsx
@@ -1120,7 +1120,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>21000</v>
+        <v>21900</v>
       </c>
       <c r="E20" s="3">
         <v>700</v>
@@ -1159,7 +1159,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-71300</v>
+        <v>-72200</v>
       </c>
       <c r="E21" s="3">
         <v>-36700</v>
@@ -1588,7 +1588,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-21000</v>
+        <v>-21900</v>
       </c>
       <c r="E32" s="3">
         <v>-700</v>
